--- a/_Docs/기획/Entropy 카드 리스트.xlsx
+++ b/_Docs/기획/Entropy 카드 리스트.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\__CrograNM\Project_Entropy\_Docs\기획\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A2934FE-3989-47E5-A6D8-6EA31B84B309}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20450CAE-0617-49E8-A0FE-A762C0A00CB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13230" yWindow="15" windowWidth="15600" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11970" yWindow="195" windowWidth="15600" windowHeight="15030" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="31">
   <si>
     <t>매직 미사일</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -63,14 +63,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Card_Base_000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> Card_Base_001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>기본 공격 카드</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -84,6 +76,78 @@
   </si>
   <si>
     <t>기본 방어 카드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card_Base_001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card_Base_003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card_Base_004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Fire</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화염구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 화염 마법</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card_Base_005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>돌풍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Wind</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 바람 마법 (밀치기)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Water</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Earth</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 물 마법</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 땅 마법 (지형생성)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card_Base_006</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>워터볼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>돌부리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Card_Base_007</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -459,7 +523,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>7</v>
@@ -494,15 +558,15 @@
         <v>1</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>8</v>
@@ -514,40 +578,88 @@
         <v>1</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
+      <c r="A6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="2">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
+      <c r="A7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="2">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
+      <c r="A8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="2">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
+      <c r="A9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" s="2">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="2"/>
